--- a/static/RegistrationFormTEMPLATE.xlsx
+++ b/static/RegistrationFormTEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\awbur\PycharmProjects\DALI_App\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1473E733-17C5-499F-9B29-87E1C4E5979F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9F9C9C-D8BD-4540-8C2C-4C893CB4B01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3010" yWindow="1860" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Name</t>
   </si>
   <si>
     <t>Age</t>
+  </si>
+  <si>
+    <t>(other fields that correspond to the online registration form…)</t>
   </si>
 </sst>
 </file>
@@ -357,20 +360,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.26953125" customWidth="1"/>
     <col min="2" max="2" width="7.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
